--- a/data/trans_camb/P59A-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 16,45</t>
+          <t>-3,59; 16,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 16,99</t>
+          <t>-2,99; 18,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 12,32</t>
+          <t>-7,22; 13,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 22,93</t>
+          <t>2,44; 22,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,91; 25,17</t>
+          <t>6,42; 26,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 17,06</t>
+          <t>-1,79; 16,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 17,59</t>
+          <t>2,03; 16,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,7; 18,81</t>
+          <t>5,26; 18,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 11,87</t>
+          <t>-1,21; 12,26</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 163,39</t>
+          <t>-20,65; 167,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,46; 169,69</t>
+          <t>-18,01; 183,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-36,74; 119,0</t>
+          <t>-37,19; 137,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 333,88</t>
+          <t>13,34; 362,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,96; 397,41</t>
+          <t>35,72; 390,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 246,59</t>
+          <t>-16,4; 240,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 186,8</t>
+          <t>9,92; 161,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,09; 189,15</t>
+          <t>29,89; 179,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 125,92</t>
+          <t>-9,49; 121,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 11,24</t>
+          <t>-3,28; 11,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 5,88</t>
+          <t>-7,46; 6,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 14,23</t>
+          <t>-1,72; 14,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 10,0</t>
+          <t>-2,25; 10,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 4,15</t>
+          <t>-8,05; 3,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 16,82</t>
+          <t>2,77; 16,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,62</t>
+          <t>-0,97; 9,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 3,34</t>
+          <t>-5,71; 3,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,69; 13,5</t>
+          <t>2,9; 14,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 153,2</t>
+          <t>-24,51; 145,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,96; 82,98</t>
+          <t>-52,77; 80,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 183,7</t>
+          <t>-15,31; 186,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 147,17</t>
+          <t>-18,98; 149,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 67,84</t>
+          <t>-59,78; 49,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,93; 245,73</t>
+          <t>17,45; 242,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 104,29</t>
+          <t>-8,51; 122,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,54; 42,3</t>
+          <t>-42,86; 50,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,22; 169,88</t>
+          <t>21,11; 177,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 4,67</t>
+          <t>-14,14; 3,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 8,51</t>
+          <t>-10,88; 9,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 4,28</t>
+          <t>-12,21; 4,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 7,65</t>
+          <t>-7,12; 8,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 6,77</t>
+          <t>-7,06; 6,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 10,54</t>
+          <t>-2,62; 10,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 3,61</t>
+          <t>-6,87; 3,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 4,96</t>
+          <t>-6,28; 5,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 5,56</t>
+          <t>-4,73; 5,86</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,96; 53,15</t>
+          <t>-66,18; 36,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,29; 86,12</t>
+          <t>-53,19; 87,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,52; 41,79</t>
+          <t>-59,62; 42,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 126,76</t>
+          <t>-58,63; 145,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,84; 120,01</t>
+          <t>-56,13; 108,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 185,89</t>
+          <t>-24,54; 185,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,47; 41,06</t>
+          <t>-46,6; 37,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 54,08</t>
+          <t>-41,41; 55,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-33,27; 68,43</t>
+          <t>-31,16; 66,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 16,22</t>
+          <t>-2,78; 15,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,28; 29,51</t>
+          <t>9,91; 29,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 23,38</t>
+          <t>-0,3; 21,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 13,26</t>
+          <t>-3,43; 13,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,44; 22,18</t>
+          <t>4,43; 21,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 7,28</t>
+          <t>-10,46; 7,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 11,29</t>
+          <t>-0,09; 12,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,29; 23,47</t>
+          <t>10,05; 23,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 10,79</t>
+          <t>-4,26; 10,94</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 139,05</t>
+          <t>-16,58; 141,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,69; 265,31</t>
+          <t>48,14; 271,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 196,47</t>
+          <t>-2,76; 195,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 132,8</t>
+          <t>-22,5; 135,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,33; 231,74</t>
+          <t>22,84; 212,04</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,26; 64,92</t>
+          <t>-60,87; 63,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 98,41</t>
+          <t>-1,34; 109,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>56,32; 208,07</t>
+          <t>58,01; 198,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-30,87; 88,8</t>
+          <t>-25,11; 86,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 6,56</t>
+          <t>-15,58; 5,76</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 3,7</t>
+          <t>-15,92; 3,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 1,55</t>
+          <t>-16,83; 2,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 12,39</t>
+          <t>-9,72; 13,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 3,88</t>
+          <t>-17,07; 3,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,48; 4,27</t>
+          <t>-14,42; 4,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 6,26</t>
+          <t>-9,72; 5,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 0,73</t>
+          <t>-13,6; 0,57</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 0,81</t>
+          <t>-13,63; 0,73</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,57; 62,14</t>
+          <t>-72,95; 47,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 38,21</t>
+          <t>-76,12; 33,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-78,98; 28,38</t>
+          <t>-76,54; 29,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,22; 132,55</t>
+          <t>-49,69; 162,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-82,27; 55,32</t>
+          <t>-81,92; 54,8</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,47; 54,58</t>
+          <t>-63,96; 59,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-46,47; 58,18</t>
+          <t>-49,62; 52,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-68,56; 8,78</t>
+          <t>-69,66; 10,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-61,34; 11,23</t>
+          <t>-64,64; 8,93</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 5,55</t>
+          <t>-16,23; 6,14</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-19,52; -0,97</t>
+          <t>-20,0; -1,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 3,03</t>
+          <t>-14,51; 3,66</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 0,95</t>
+          <t>-15,7; -0,06</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 0,48</t>
+          <t>-14,68; 0,41</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 8,08</t>
+          <t>-7,55; 8,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 0,03</t>
+          <t>-12,75; -0,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-13,56; -2,02</t>
+          <t>-14,78; -2,52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 4,15</t>
+          <t>-8,86; 3,64</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-70,74; 58,47</t>
+          <t>-72,85; 54,21</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-84,71; -3,73</t>
+          <t>-84,72; -9,12</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 28,66</t>
+          <t>-63,06; 33,11</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-84,65; 23,8</t>
+          <t>-83,55; 15,32</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-85,11; 15,59</t>
+          <t>-81,37; 17,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-47,25; 97,32</t>
+          <t>-44,24; 105,3</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-69,43; 2,88</t>
+          <t>-71,23; 2,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-75,23; -17,28</t>
+          <t>-76,96; -19,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-44,22; 39,05</t>
+          <t>-47,69; 32,59</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 9,73</t>
+          <t>-4,22; 9,88</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 10,25</t>
+          <t>-3,45; 10,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 8,93</t>
+          <t>-5,53; 8,78</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,28; 14,87</t>
+          <t>3,0; 14,87</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 8,66</t>
+          <t>-2,16; 8,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,86; 12,13</t>
+          <t>1,57; 11,97</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,93; 10,52</t>
+          <t>1,56; 10,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 7,72</t>
+          <t>-0,58; 7,7</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,01; 8,78</t>
+          <t>0,15; 8,99</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,48; 93,06</t>
+          <t>-24,49; 96,41</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 93,99</t>
+          <t>-19,73; 94,21</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 78,98</t>
+          <t>-30,51; 81,5</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22,14; 225,19</t>
+          <t>21,66; 241,9</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 157,3</t>
+          <t>-19,38; 140,36</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,65; 189,56</t>
+          <t>13,49; 186,25</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,54; 115,39</t>
+          <t>10,13; 116,08</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 83,12</t>
+          <t>-3,89; 84,74</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 94,72</t>
+          <t>1,05; 98,64</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 7,04</t>
+          <t>-3,92; 6,74</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 10,35</t>
+          <t>0,17; 11,05</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 7,74</t>
+          <t>-3,66; 7,41</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 8,26</t>
+          <t>-1,74; 8,08</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,67</t>
+          <t>1,2; 11,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,92; -0,1</t>
+          <t>-7,14; 0,42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 6,59</t>
+          <t>-1,07; 6,22</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,37</t>
+          <t>1,99; 9,62</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,98</t>
+          <t>-4,64; 2,11</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 91,62</t>
+          <t>-32,0; 85,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 129,69</t>
+          <t>-1,67; 138,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 95,69</t>
+          <t>-29,67; 91,51</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 149,33</t>
+          <t>-19,02; 143,64</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,69; 200,95</t>
+          <t>6,59; 206,92</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-72,6; 3,56</t>
+          <t>-71,61; 11,78</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 89,03</t>
+          <t>-10,85; 88,26</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>19,33; 124,71</t>
+          <t>17,15; 127,97</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-41,95; 28,7</t>
+          <t>-42,65; 31,96</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,43</t>
+          <t>-1,26; 4,41</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,94; 6,69</t>
+          <t>1,02; 6,86</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 5,04</t>
+          <t>-0,73; 5,32</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,58</t>
+          <t>1,47; 6,43</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,24</t>
+          <t>1,35; 6,41</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,29</t>
+          <t>0,26; 5,03</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,84</t>
+          <t>0,97; 4,89</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,52</t>
+          <t>1,98; 5,88</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,58</t>
+          <t>0,35; 4,53</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 35,88</t>
+          <t>-8,68; 35,19</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>6,01; 54,02</t>
+          <t>6,58; 55,96</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 42,66</t>
+          <t>-5,0; 42,05</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>12,17; 73,14</t>
+          <t>13,07; 70,5</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>12,29; 69,16</t>
+          <t>9,82; 69,39</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,15; 58,72</t>
+          <t>2,26; 55,72</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,45; 43,53</t>
+          <t>8,12; 46,17</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>14,71; 50,55</t>
+          <t>15,87; 55,81</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>4,71; 41,67</t>
+          <t>2,5; 41,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P59A-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,96</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,43</t>
+          <t>6,71</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>4,88</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 16,13</t>
+          <t>-3,82; 16,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 18,58</t>
+          <t>-3,46; 16,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 13,26</t>
+          <t>-6,69; 12,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 22,52</t>
+          <t>1,04; 22,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,42; 26,15</t>
+          <t>5,47; 24,86</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 16,51</t>
+          <t>-1,67; 14,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 16,36</t>
+          <t>2,65; 17,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 18,43</t>
+          <t>4,39; 18,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 12,26</t>
+          <t>-1,57; 10,99</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>37,62%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 167,07</t>
+          <t>-22,12; 155,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,01; 183,36</t>
+          <t>-20,8; 171,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-37,19; 137,23</t>
+          <t>-32,96; 130,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 362,91</t>
+          <t>4,03; 307,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,72; 390,48</t>
+          <t>29,25; 353,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 240,02</t>
+          <t>-12,58; 209,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 161,17</t>
+          <t>14,64; 178,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>29,89; 179,7</t>
+          <t>25,99; 198,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 121,62</t>
+          <t>-12,03; 117,34</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,58</t>
+          <t>7,48</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,89</t>
+          <t>9,63</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,2</t>
+          <t>8,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 11,83</t>
+          <t>-2,37; 11,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 6,09</t>
+          <t>-7,56; 5,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 14,84</t>
+          <t>-0,45; 16,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 10,38</t>
+          <t>-2,95; 10,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 3,25</t>
+          <t>-7,99; 4,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,77; 16,3</t>
+          <t>3,22; 16,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 9,31</t>
+          <t>-0,72; 8,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 3,73</t>
+          <t>-5,74; 3,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 14,16</t>
+          <t>3,21; 13,73</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 145,34</t>
+          <t>-20,3; 154,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,77; 80,92</t>
+          <t>-53,4; 69,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 186,58</t>
+          <t>-7,31; 203,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 149,22</t>
+          <t>-27,1; 150,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-59,78; 49,9</t>
+          <t>-59,19; 63,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,45; 242,74</t>
+          <t>19,87; 233,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 122,54</t>
+          <t>-6,0; 106,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,86; 50,02</t>
+          <t>-41,98; 42,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,11; 177,71</t>
+          <t>21,07; 160,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,88</t>
+          <t>-2,31</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>4,28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>1,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 3,4</t>
+          <t>-13,32; 4,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 9,29</t>
+          <t>-9,87; 9,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 4,09</t>
+          <t>-11,2; 6,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 8,49</t>
+          <t>-6,72; 8,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 6,23</t>
+          <t>-6,69; 6,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 10,59</t>
+          <t>-2,35; 10,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 3,34</t>
+          <t>-7,77; 3,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,25</t>
+          <t>-6,64; 5,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 5,86</t>
+          <t>-4,23; 6,6</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-24,87%</t>
+          <t>-14,8%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 36,52</t>
+          <t>-63,99; 44,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 87,19</t>
+          <t>-47,9; 92,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,62; 42,36</t>
+          <t>-53,93; 55,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,63; 145,15</t>
+          <t>-57,16; 165,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,13; 108,1</t>
+          <t>-53,71; 131,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 185,45</t>
+          <t>-20,99; 177,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 37,93</t>
+          <t>-50,95; 43,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,41; 55,34</t>
+          <t>-42,7; 56,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 66,84</t>
+          <t>-28,0; 69,73</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,71</t>
+          <t>9,74</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>4,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,76</t>
+          <t>6,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 15,87</t>
+          <t>-2,11; 17,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,91; 29,87</t>
+          <t>10,42; 30,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 21,91</t>
+          <t>-1,38; 20,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 13,21</t>
+          <t>-3,93; 12,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,43; 21,2</t>
+          <t>4,71; 21,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 7,24</t>
+          <t>-3,55; 11,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 12,29</t>
+          <t>-0,52; 12,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,05; 23,12</t>
+          <t>9,56; 22,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 10,94</t>
+          <t>1,1; 13,51</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,04%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 141,46</t>
+          <t>-12,34; 180,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>48,14; 271,22</t>
+          <t>49,39; 285,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 195,2</t>
+          <t>-7,65; 191,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 135,27</t>
+          <t>-23,91; 132,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>22,84; 212,04</t>
+          <t>25,92; 238,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 63,66</t>
+          <t>-22,29; 115,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 109,37</t>
+          <t>-3,7; 107,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>58,01; 198,68</t>
+          <t>54,96; 197,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 86,74</t>
+          <t>5,51; 116,93</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,24</t>
+          <t>-7,82</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-3,49</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-5,74</t>
+          <t>-5,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 5,76</t>
+          <t>-15,38; 6,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 3,64</t>
+          <t>-16,06; 4,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 2,2</t>
+          <t>-17,05; 1,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 13,12</t>
+          <t>-11,23; 11,85</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 3,49</t>
+          <t>-17,11; 2,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 4,43</t>
+          <t>-13,56; 5,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 5,92</t>
+          <t>-9,16; 5,88</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 0,57</t>
+          <t>-13,2; 0,89</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 0,73</t>
+          <t>-12,5; 1,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-43,92%</t>
+          <t>-47,43%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-27,97%</t>
+          <t>-23,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-36,54%</t>
+          <t>-36,44%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-72,95; 47,84</t>
+          <t>-72,11; 64,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-76,12; 33,8</t>
+          <t>-75,81; 41,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-76,54; 29,74</t>
+          <t>-77,92; 19,98</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-49,69; 162,29</t>
+          <t>-52,1; 133,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-81,92; 54,8</t>
+          <t>-82,13; 53,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-63,96; 59,1</t>
+          <t>-61,28; 68,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 52,55</t>
+          <t>-46,32; 51,77</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 10,27</t>
+          <t>-68,09; 12,01</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 8,93</t>
+          <t>-61,49; 11,49</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-5,1</t>
+          <t>-4,49</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-1,88</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 6,14</t>
+          <t>-15,81; 5,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-20,0; -1,36</t>
+          <t>-18,39; -0,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 3,66</t>
+          <t>-13,51; 3,86</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-15,7; -0,06</t>
+          <t>-14,73; -0,16</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-14,68; 0,41</t>
+          <t>-14,22; 0,39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 8,5</t>
+          <t>-6,96; 8,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-12,75; -0,09</t>
+          <t>-12,72; 0,02</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,78; -2,52</t>
+          <t>-13,75; -2,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 3,64</t>
+          <t>-7,95; 4,16</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-29,91%</t>
+          <t>-26,32%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-14,32%</t>
+          <t>-12,65%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-72,85; 54,21</t>
+          <t>-71,1; 56,13</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-84,72; -9,12</t>
+          <t>-81,0; -1,37</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,06; 33,11</t>
+          <t>-58,89; 36,05</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-83,55; 15,32</t>
+          <t>-84,5; 5,67</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 17,57</t>
+          <t>-83,78; 17,85</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 105,3</t>
+          <t>-40,81; 123,75</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-71,23; 2,56</t>
+          <t>-69,62; 9,8</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-76,96; -19,25</t>
+          <t>-76,53; -17,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-47,69; 32,59</t>
+          <t>-43,32; 37,71</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,1</t>
+          <t>2,8</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,86</t>
+          <t>8,1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>5,59</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,88</t>
+          <t>-3,47; 10,01</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 10,07</t>
+          <t>-3,12; 10,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 8,78</t>
+          <t>-4,48; 9,16</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,0; 14,87</t>
+          <t>3,11; 15,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 8,41</t>
+          <t>-1,79; 7,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,97</t>
+          <t>2,51; 13,2</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,56; 10,34</t>
+          <t>1,28; 10,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 7,7</t>
+          <t>-0,77; 7,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,15; 8,99</t>
+          <t>1,12; 9,41</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 96,41</t>
+          <t>-19,57; 99,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,73; 94,21</t>
+          <t>-18,34; 91,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-30,51; 81,5</t>
+          <t>-24,76; 85,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,66; 241,9</t>
+          <t>21,36; 252,83</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 140,36</t>
+          <t>-15,92; 129,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,49; 186,25</t>
+          <t>21,24; 209,69</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,13; 116,08</t>
+          <t>6,85; 110,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 84,74</t>
+          <t>-7,46; 82,54</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,05; 98,64</t>
+          <t>8,51; 100,63</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>2,22</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>-3,21</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-0,77</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 6,74</t>
+          <t>-3,55; 6,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,17; 11,05</t>
+          <t>-0,05; 10,62</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 7,41</t>
+          <t>-3,46; 7,9</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 8,08</t>
+          <t>-1,27; 8,21</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,08</t>
+          <t>1,36; 10,9</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 0,42</t>
+          <t>-7,43; 0,36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 6,22</t>
+          <t>-1,4; 5,99</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,62</t>
+          <t>1,86; 9,31</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,11</t>
+          <t>-3,85; 2,63</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-45,92%</t>
+          <t>-42,31%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-12,12%</t>
+          <t>-8,55%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 85,63</t>
+          <t>-28,85; 83,46</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 138,23</t>
+          <t>-1,97; 132,64</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-29,67; 91,51</t>
+          <t>-26,77; 96,66</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 143,64</t>
+          <t>-14,27; 152,83</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,59; 206,92</t>
+          <t>8,68; 195,57</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-71,61; 11,78</t>
+          <t>-71,03; 9,29</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 88,26</t>
+          <t>-12,09; 78,84</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>17,15; 127,97</t>
+          <t>15,99; 126,03</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-42,65; 31,96</t>
+          <t>-35,87; 35,87</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>3,1</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,41</t>
+          <t>-1,2; 4,45</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,86</t>
+          <t>0,95; 6,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,32</t>
+          <t>-0,08; 5,7</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,43</t>
+          <t>1,18; 6,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,41</t>
+          <t>1,48; 6,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,03</t>
+          <t>1,19; 5,83</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,89</t>
+          <t>0,82; 4,62</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,88</t>
+          <t>1,93; 5,64</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,53</t>
+          <t>1,29; 4,95</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 35,19</t>
+          <t>-8,1; 36,54</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>6,58; 55,96</t>
+          <t>6,22; 54,06</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 42,05</t>
+          <t>-1,15; 46,8</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13,07; 70,5</t>
+          <t>9,89; 71,14</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>9,82; 69,39</t>
+          <t>12,48; 68,26</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,26; 55,72</t>
+          <t>10,21; 66,18</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,12; 46,17</t>
+          <t>6,21; 41,56</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>15,87; 55,81</t>
+          <t>15,01; 51,18</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2,5; 41,15</t>
+          <t>10,47; 45,55</t>
         </is>
       </c>
     </row>
